--- a/InputData/hydgn/HPPECbP/Hydgn Prod Perc Excess Cap by Pathway.xlsx
+++ b/InputData/hydgn/HPPECbP/Hydgn Prod Perc Excess Cap by Pathway.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\hydgn\HPPECbP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\HPPECbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DAFAF3-1966-4FD0-8809-7F59B118CB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1010B8-D415-47AB-9959-B7809600643F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="HPPECbP" sheetId="2" r:id="rId2"/>
+    <sheet name="Capacity Factors" sheetId="3" r:id="rId2"/>
+    <sheet name="HPPECbP" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,44 +38,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>Wang et al.</t>
-  </si>
-  <si>
-    <t>Quantifying the flexibility of hydrogen production systems to support large-scale renewable energy integration</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.jpowsour.2018.07.101</t>
-  </si>
-  <si>
-    <t>Page 388, Table 2</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Tested scenarios include 100% capacity (no excess),</t>
-  </si>
-  <si>
-    <t>125% capacity, and 150% capacity.  We choose to use</t>
-  </si>
-  <si>
-    <t>the median scenario (125% capacity, or 25% excess).</t>
-  </si>
-  <si>
     <t>HPPECbP Hydrogen Production Percent Excess Capacity by Pathway</t>
   </si>
   <si>
-    <t>We use this value for all pathways, though the</t>
-  </si>
-  <si>
-    <t>study only concerned electrolyzers.</t>
-  </si>
-  <si>
     <t>electrolysis</t>
   </si>
   <si>
@@ -87,9 +58,6 @@
     <t>biomass gasification</t>
   </si>
   <si>
-    <t>thermochemical water splitting</t>
-  </si>
-  <si>
     <t>Excess Capacity (dimensionless)</t>
   </si>
   <si>
@@ -97,6 +65,93 @@
   </si>
   <si>
     <t>natural gas reforming with CCS</t>
+  </si>
+  <si>
+    <t>hydrocarbon partial oxidation</t>
+  </si>
+  <si>
+    <t>Pathway</t>
+  </si>
+  <si>
+    <t>Capacity factor (annual output / full-load output)</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Green electrolysis inputs (DOE 24005, as used in hydgn/HPEC)</t>
+  </si>
+  <si>
+    <t>Nameplate production (kg/yr)</t>
+  </si>
+  <si>
+    <t>DOE plant size used in HPEC (kW)</t>
+  </si>
+  <si>
+    <t>Lifetime-average electricity use (kWh/kg)</t>
+  </si>
+  <si>
+    <t>Capacity factor HPEC previously divided by (class-1 wind)</t>
+  </si>
+  <si>
+    <t>Hours per year</t>
+  </si>
+  <si>
+    <t>DOE Hydrogen Program Record 24005 (2024), Table 2, Grid - Average Scenario</t>
+  </si>
+  <si>
+    <t>NETL 2022 (DOE/NETL-2022/3241), Exhibit ES-2, Case 1 SMR</t>
+  </si>
+  <si>
+    <t>NETL 2022, Exhibit ES-2, Cases 4-5 (Shell gasifier)</t>
+  </si>
+  <si>
+    <t>NETL 2022, Exhibit ES-2, Case 6 (coal/biomass co-gasification)</t>
+  </si>
+  <si>
+    <t>Default: NETL 2022 reforming cases (SMR/ATR) all use 90%</t>
+  </si>
+  <si>
+    <t>Utilization implied by the earlier HPEC derivation (DOE 24005 106 MW / 0.51 CF for 18.25 Mkg/yr at 57.5 kWh/kg); equals hydgn/HPEC 'DoE Data'!B89. Kept so the green cost is unchanged (DOE 24005 hybrid wind-PV sizing, 50% of VRE nameplate).</t>
+  </si>
+  <si>
+    <t>NETL 2022, Exhibit ES-2, Case 2 SMR with CCS</t>
+  </si>
+  <si>
+    <t>See the 'Capacity Factors' tab (DOE Hydrogen Program Record 24005; NETL 2022 DOE/NETL-2022/3241)</t>
+  </si>
+  <si>
+    <t>Notes (revised 2026-10-23, bug B8)</t>
+  </si>
+  <si>
+    <t>HPPECbP is the single utilization parameter for hydrogen production. Hydrogen production capacity in</t>
+  </si>
+  <si>
+    <t>EPS is measured as annual output, and HPEC/HPEO costs are per unit of full-load (100% CF) capacity, so</t>
+  </si>
+  <si>
+    <t>the capacity a plant must build per unit of annual output is 1/CF = 1 + HPPECbP, i.e. HPPECbP = 1/CF - 1.</t>
+  </si>
+  <si>
+    <t>EPS multiplies HPEC CapEx and OpEx by (1 + HPPECbP) in the levelized cost used for pathway choice, in</t>
+  </si>
+  <si>
+    <t>the dispatch cost, and in capital and O&amp;M spending. For grid electrolysis it also sizes the spare</t>
+  </si>
+  <si>
+    <t>capacity that provides demand response (Demand Responsive Electricity Capacity for Electrolyzers).</t>
+  </si>
+  <si>
+    <t>The earlier value (25% for every pathway, from Wang et al. 2018, an electrolyzer flexibility study) was</t>
+  </si>
+  <si>
+    <t>applied to spending only, while the electrolyzer CapEx input had a 51% CF already divided in.</t>
+  </si>
+  <si>
+    <t>If the green or grid CF changes, change the matching CF cell in hydgn/HPEC 'DoE Data' (B88, B89),</t>
+  </si>
+  <si>
+    <t>which drives stack-replacement timing.</t>
   </si>
 </sst>
 </file>
@@ -440,12 +495,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -453,69 +508,209 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
+      <c r="B6" s="3"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D45B9FA1-0082-4FB6-9570-4653F98A534A}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>0.97</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>18250000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>0.9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>8760</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <f>F5*F2*F4/(F3*F6)</f>
+        <v>0.57635613207547165</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>0.9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
@@ -529,7 +724,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B1" s="4">
         <v>2017</v>
@@ -636,988 +831,989 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="C2">
-        <f>$B$2</f>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:AI6" si="0">$B$2</f>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="E2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="F2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="G2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="H2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="I2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="J2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="K2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="L2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="M2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="N2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="O2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="Q2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="R2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="S2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="T2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="U2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="V2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="W2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="X2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="AB2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="AC2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="AD2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="AE2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="AF2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="AG2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="AH2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
       <c r="AI2">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$2-1</f>
+        <v>3.0927835051546504E-2</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:Q8" si="1">$B$2</f>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="C3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="D3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="E3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="F3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="G3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="H3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="I3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="J3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="K3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="L3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="M3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="N3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="O3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="P3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="R3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="S3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="T3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="U3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="V3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="W3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="X3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AC3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AD3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$3-1</f>
+        <v>0.11111111111111116</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <f t="shared" si="1"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="C4">
-        <f t="shared" si="1"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="L4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="M4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="N4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="O4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="P4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="R4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="S4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="T4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="U4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="V4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="W4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="X4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$4-1</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <f t="shared" si="1"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="C5">
-        <f t="shared" si="1"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="G5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="H5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="I5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="L5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="M5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="N5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="O5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="P5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="R5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="S5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="T5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="U5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="V5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="W5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="X5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="AE5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="AG5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="AH5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="0"/>
+        <f>1/'Capacity Factors'!$B$5-1</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="C6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="D6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="F6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="H6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="P6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="R6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="S6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="T6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="U6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="V6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="W6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="X6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$6-1</f>
+        <v>0.11111111111111116</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="C7">
-        <f t="shared" ref="C7:AI8" si="2">$B$2</f>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="D7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="E7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="F7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="G7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="H7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="I7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="J7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="K7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="L7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="M7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="N7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="O7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="P7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="R7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="S7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="T7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="U7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="V7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="W7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="X7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="AG7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$7-1</f>
+        <v>0.73503836317135574</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="C8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="D8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="E8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="F8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="G8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="H8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="I8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="J8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="K8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="L8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="M8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="N8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="O8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="P8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="R8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="S8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="T8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="U8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="V8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="W8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="X8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f>1/'Capacity Factors'!$B$8-1</f>
+        <v>0.11111111111111116</v>
       </c>
     </row>
   </sheetData>
